--- a/Fibre_data_V6.xlsx
+++ b/Fibre_data_V6.xlsx
@@ -9,9 +9,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawm\VSCode Projects\GlassMechAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95283F9E-AD33-4DA1-9B9E-50EDEBB16BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F736B55F-8F9D-4E2F-B78D-3C76DE0D2F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2220" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="126">
   <si>
     <t>test_num</t>
   </si>
@@ -79,9 +79,6 @@
     <t>S1.5</t>
   </si>
   <si>
-    <t>outlier diameter</t>
-  </si>
-  <si>
     <t>S1.6</t>
   </si>
   <si>
@@ -94,9 +91,6 @@
     <t>S1.9</t>
   </si>
   <si>
-    <t>maybe error</t>
-  </si>
-  <si>
     <t>S1.10</t>
   </si>
   <si>
@@ -419,6 +413,9 @@
   </si>
   <si>
     <t>Diameter (mm)</t>
+  </si>
+  <si>
+    <t>outlier</t>
   </si>
 </sst>
 </file>
@@ -779,10 +776,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -803,13 +800,13 @@
         <v>6</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -843,7 +840,7 @@
         <v>21.594158152105603</v>
       </c>
       <c r="J2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -880,7 +877,7 @@
         <v>26.066110693145063</v>
       </c>
       <c r="J3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -917,7 +914,7 @@
         <v>24.94492104370029</v>
       </c>
       <c r="J4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -954,7 +951,7 @@
         <v>41.311729947835417</v>
       </c>
       <c r="J5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -991,10 +988,10 @@
         <v>65.394998895016101</v>
       </c>
       <c r="J6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K6" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -1009,7 +1006,7 @@
         <v>S1</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="3">
         <v>3.6222222222222218E-2</v>
@@ -1031,7 +1028,7 @@
         <v>25.082338613260362</v>
       </c>
       <c r="J7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -1046,7 +1043,7 @@
         <v>S1</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="3">
         <v>3.3888888888888892E-2</v>
@@ -1068,7 +1065,7 @@
         <v>25.707579985348239</v>
       </c>
       <c r="J8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -1083,7 +1080,7 @@
         <v>S1</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="3">
         <v>3.9666666666666663E-2</v>
@@ -1105,7 +1102,7 @@
         <v>21.08434245619274</v>
       </c>
       <c r="J9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -1120,7 +1117,7 @@
         <v>S2</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="3">
         <v>4.5888888888888882E-2</v>
@@ -1142,10 +1139,10 @@
         <v>22.862520565210851</v>
       </c>
       <c r="J10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K10" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -1160,7 +1157,7 @@
         <v>S1</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D11" s="3">
         <v>3.6333333333333336E-2</v>
@@ -1182,7 +1179,7 @@
         <v>22.88066438059986</v>
       </c>
       <c r="J11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -1197,7 +1194,7 @@
         <v>S2</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D12" s="3">
         <v>4.6777777777777772E-2</v>
@@ -1219,10 +1216,10 @@
         <v>29.270179379141904</v>
       </c>
       <c r="J12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K12" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -1237,7 +1234,7 @@
         <v>S1</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D13" s="3">
         <v>0.04</v>
@@ -1259,7 +1256,7 @@
         <v>26.905943325371005</v>
       </c>
       <c r="J13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -1274,7 +1271,7 @@
         <v>S1</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D14" s="3">
         <v>2.0999999999999998E-2</v>
@@ -1296,10 +1293,10 @@
         <v>70.075043264159291</v>
       </c>
       <c r="J14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K14" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="L14">
         <v>1</v>
@@ -1314,7 +1311,7 @@
         <v>S1</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D15" s="3">
         <v>3.833333333333333E-2</v>
@@ -1336,7 +1333,7 @@
         <v>24.758985355391612</v>
       </c>
       <c r="J15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -1351,7 +1348,7 @@
         <v>S1</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D16" s="3">
         <v>4.2999999999999997E-2</v>
@@ -1373,7 +1370,7 @@
         <v>25.714706523989104</v>
       </c>
       <c r="J16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L16">
         <v>1</v>
@@ -1388,7 +1385,7 @@
         <v>S1</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D17" s="3">
         <v>3.177777777777778E-2</v>
@@ -1410,7 +1407,7 @@
         <v>29.12360457413147</v>
       </c>
       <c r="J17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L17">
         <v>1</v>
@@ -1425,7 +1422,7 @@
         <v>S1</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D18" s="3">
         <v>3.3888888888888885E-2</v>
@@ -1447,7 +1444,7 @@
         <v>26.250619559679848</v>
       </c>
       <c r="J18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L18">
         <v>1</v>
@@ -1462,7 +1459,7 @@
         <v>S1</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D19" s="3">
         <v>4.1999999999999996E-2</v>
@@ -1484,7 +1481,7 @@
         <v>27.104134927958121</v>
       </c>
       <c r="J19" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L19">
         <v>2</v>
@@ -1499,7 +1496,7 @@
         <v>S1</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D20" s="3">
         <v>4.4111111111111101E-2</v>
@@ -1521,10 +1518,10 @@
         <v>27.993875423027184</v>
       </c>
       <c r="J20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K20" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="L20">
         <v>2</v>
@@ -1539,7 +1536,7 @@
         <v>S2</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D21" s="3">
         <v>4.6777777777777772E-2</v>
@@ -1561,7 +1558,7 @@
         <v>31.5644754538984</v>
       </c>
       <c r="J21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L21">
         <v>2</v>
@@ -1576,7 +1573,7 @@
         <v>S1</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D22" s="3">
         <v>3.5999999999999997E-2</v>
@@ -1598,7 +1595,7 @@
         <v>23.5457785309762</v>
       </c>
       <c r="J22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22">
@@ -1614,7 +1611,7 @@
         <v>S1</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D23" s="3">
         <v>3.8777777777777772E-2</v>
@@ -1636,7 +1633,7 @@
         <v>28.069649315094384</v>
       </c>
       <c r="J23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23">
@@ -1652,7 +1649,7 @@
         <v>S1</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D24" s="3">
         <v>4.2222222222222217E-2</v>
@@ -1674,7 +1671,7 @@
         <v>29.090362762393777</v>
       </c>
       <c r="J24" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L24">
         <v>2</v>
@@ -1689,7 +1686,7 @@
         <v>S1</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D25" s="3">
         <v>4.1666666666666664E-2</v>
@@ -1711,7 +1708,7 @@
         <v>29.758806538197135</v>
       </c>
       <c r="J25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L25">
         <v>2</v>
@@ -1726,7 +1723,7 @@
         <v>S2</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D26" s="3">
         <v>5.8666666666666673E-2</v>
@@ -1748,7 +1745,7 @@
         <v>27.607217016561663</v>
       </c>
       <c r="J26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L26">
         <v>2</v>
@@ -1763,7 +1760,7 @@
         <v>S2</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D27" s="3">
         <v>5.8777777777777783E-2</v>
@@ -1785,7 +1782,7 @@
         <v>25.454124184719092</v>
       </c>
       <c r="J27" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L27">
         <v>2</v>
@@ -1800,7 +1797,7 @@
         <v>S2</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D28" s="3">
         <v>7.7333333333333323E-2</v>
@@ -1822,7 +1819,7 @@
         <v>24.469824116475465</v>
       </c>
       <c r="J28" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L28">
         <v>2</v>
@@ -1837,7 +1834,7 @@
         <v>S2</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D29" s="3">
         <v>6.6444444444444459E-2</v>
@@ -1859,7 +1856,7 @@
         <v>14.06223218890819</v>
       </c>
       <c r="J29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L29">
         <v>2</v>
@@ -1874,7 +1871,7 @@
         <v>S2</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D30" s="3">
         <v>5.255555555555555E-2</v>
@@ -1896,7 +1893,7 @@
         <v>22.698020546351628</v>
       </c>
       <c r="J30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L30">
         <v>2</v>
@@ -1911,7 +1908,7 @@
         <v>S2</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D31" s="3">
         <v>5.6555555555555553E-2</v>
@@ -1933,7 +1930,7 @@
         <v>35.954754188306111</v>
       </c>
       <c r="J31" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L31">
         <v>2</v>
@@ -1948,7 +1945,7 @@
         <v>S2</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D32" s="3">
         <v>6.1222222222222213E-2</v>
@@ -1970,7 +1967,7 @@
         <v>25.841981625179663</v>
       </c>
       <c r="J32" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L32">
         <v>2</v>
@@ -1985,7 +1982,7 @@
         <v>S2</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D33" s="3">
         <v>6.0444444444444446E-2</v>
@@ -2007,7 +2004,7 @@
         <v>27.323267542671847</v>
       </c>
       <c r="J33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L33">
         <v>2</v>
@@ -2022,7 +2019,7 @@
         <v>S2</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D34" s="3">
         <v>7.1222222222222228E-2</v>
@@ -2044,7 +2041,7 @@
         <v>24.435472130301214</v>
       </c>
       <c r="J34" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L34">
         <v>2</v>
@@ -2055,10 +2052,10 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D35" s="3">
         <v>0.109349222222222</v>
@@ -2067,7 +2064,7 @@
         <v>3.0256204643749436E-3</v>
       </c>
       <c r="F35" s="7">
-        <f>(D35/2)^2 * PI()</f>
+        <f t="shared" ref="F35:F44" si="3">(D35/2)^2 * PI()</f>
         <v>9.3912040747148092E-3</v>
       </c>
       <c r="G35" s="5">
@@ -2080,7 +2077,7 @@
         <v>29.070798882196591</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -2088,10 +2085,10 @@
         <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C36" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D36" s="3">
         <v>9.2363000000000001E-2</v>
@@ -2100,7 +2097,7 @@
         <v>1.7346506852966136E-3</v>
       </c>
       <c r="F36" s="7">
-        <f>(D36/2)^2 * PI()</f>
+        <f t="shared" si="3"/>
         <v>6.7001718602562373E-3</v>
       </c>
       <c r="G36" s="5">
@@ -2113,7 +2110,7 @@
         <v>33.986438947588276</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -2121,10 +2118,10 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D37" s="3">
         <v>8.839844444444446E-2</v>
@@ -2133,7 +2130,7 @@
         <v>1.8052824648175621E-3</v>
       </c>
       <c r="F37" s="7">
-        <f>(D37/2)^2 * PI()</f>
+        <f t="shared" si="3"/>
         <v>6.1373250717114084E-3</v>
       </c>
       <c r="G37" s="5">
@@ -2146,7 +2143,7 @@
         <v>31.925463471833247</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -2154,10 +2151,10 @@
         <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C38" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D38" s="3">
         <v>5.9569888888888874E-2</v>
@@ -2166,7 +2163,7 @@
         <v>4.287168950614274E-3</v>
       </c>
       <c r="F38" s="7">
-        <f>(D38/2)^2 * PI()</f>
+        <f t="shared" si="3"/>
         <v>2.7870416662032584E-3</v>
       </c>
       <c r="G38" s="5">
@@ -2179,7 +2176,7 @@
         <v>27.669905320764421</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -2187,10 +2184,10 @@
         <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D39" s="3">
         <v>0.10065266666666668</v>
@@ -2199,7 +2196,7 @@
         <v>1.2020938212136359E-2</v>
       </c>
       <c r="F39" s="7">
-        <f>(D39/2)^2 * PI()</f>
+        <f t="shared" si="3"/>
         <v>7.956836833259354E-3</v>
       </c>
       <c r="G39" s="5">
@@ -2212,7 +2209,7 @@
         <v>24.373739978323556</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -2220,10 +2217,10 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C40" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D40" s="3">
         <v>0.12231700000000001</v>
@@ -2232,7 +2229,7 @@
         <v>1.716861260410988E-2</v>
       </c>
       <c r="F40" s="7">
-        <f>(D40/2)^2 * PI()</f>
+        <f t="shared" si="3"/>
         <v>1.1750694165026129E-2</v>
       </c>
       <c r="G40" s="5">
@@ -2245,7 +2242,7 @@
         <v>22.309630026082594</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -2253,10 +2250,10 @@
         <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D41" s="3">
         <v>0.16096522222222223</v>
@@ -2265,7 +2262,7 @@
         <v>7.0442515176876276E-3</v>
       </c>
       <c r="F41" s="7">
-        <f>(D41/2)^2 * PI()</f>
+        <f t="shared" si="3"/>
         <v>2.0349511505659914E-2</v>
       </c>
       <c r="G41" s="5">
@@ -2278,7 +2275,7 @@
         <v>26.27653424042235</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -2286,10 +2283,10 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D42" s="3">
         <v>0.11886566666666666</v>
@@ -2298,7 +2295,7 @@
         <v>2.2819855937319168E-3</v>
       </c>
       <c r="F42" s="7">
-        <f>(D42/2)^2 * PI()</f>
+        <f t="shared" si="3"/>
         <v>1.1096927338248821E-2</v>
       </c>
       <c r="G42" s="5">
@@ -2311,7 +2308,7 @@
         <v>24.707432872571466</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
@@ -2319,10 +2316,10 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D43" s="3">
         <v>7.6555444444444454E-2</v>
@@ -2331,7 +2328,7 @@
         <v>3.3079085201646341E-3</v>
       </c>
       <c r="F43" s="7">
-        <f>(D43/2)^2 * PI()</f>
+        <f t="shared" si="3"/>
         <v>4.6030113487446466E-3</v>
       </c>
       <c r="G43" s="5">
@@ -2344,7 +2341,7 @@
         <v>26.672176930104111</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
@@ -2352,10 +2349,10 @@
         <v>10</v>
       </c>
       <c r="B44" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C44" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D44" s="3">
         <v>9.0440666666666669E-2</v>
@@ -2364,7 +2361,7 @@
         <v>5.6683407625159592E-3</v>
       </c>
       <c r="F44" s="7">
-        <f>(D44/2)^2 * PI()</f>
+        <f t="shared" si="3"/>
         <v>6.4241754200404398E-3</v>
       </c>
       <c r="G44" s="5">
@@ -2377,7 +2374,7 @@
         <v>48.954166606205234</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
@@ -2389,7 +2386,7 @@
         <v>L1</v>
       </c>
       <c r="C45" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D45" s="3">
         <v>0.18255555555555555</v>
@@ -2411,7 +2408,7 @@
         <v>32.252038189113591</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -2419,11 +2416,11 @@
         <v>4</v>
       </c>
       <c r="B46" t="str">
-        <f t="shared" ref="B46:B54" si="3">IF(D46&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" ref="B46:B54" si="4">IF(D46&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
         <v>L1</v>
       </c>
       <c r="C46" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D46" s="3">
         <v>0.19422222222222221</v>
@@ -2445,7 +2442,7 @@
         <v>26.963167015998369</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
@@ -2453,11 +2450,11 @@
         <v>7</v>
       </c>
       <c r="B47" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>L1</v>
       </c>
       <c r="C47" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D47" s="3">
         <v>0.2048888888888889</v>
@@ -2479,7 +2476,7 @@
         <v>25.246929866657489</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
@@ -2487,11 +2484,11 @@
         <v>8</v>
       </c>
       <c r="B48" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>L1</v>
       </c>
       <c r="C48" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D48" s="3">
         <v>0.21011111111111111</v>
@@ -2513,7 +2510,7 @@
         <v>28.584503410928303</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
@@ -2521,11 +2518,11 @@
         <v>9</v>
       </c>
       <c r="B49" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>L1</v>
       </c>
       <c r="C49" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D49" s="3">
         <v>0.2048888888888889</v>
@@ -2547,7 +2544,7 @@
         <v>26.152900044242092</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
@@ -2555,11 +2552,11 @@
         <v>10</v>
       </c>
       <c r="B50" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>L1</v>
       </c>
       <c r="C50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D50" s="3">
         <v>0.17555555555555555</v>
@@ -2581,7 +2578,7 @@
         <v>29.924169062852872</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
@@ -2589,11 +2586,11 @@
         <v>11</v>
       </c>
       <c r="B51" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>L1</v>
       </c>
       <c r="C51" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D51" s="3">
         <v>0.17933333333333332</v>
@@ -2615,7 +2612,7 @@
         <v>27.544668393322667</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
@@ -2623,11 +2620,11 @@
         <v>12</v>
       </c>
       <c r="B52" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>L1</v>
       </c>
       <c r="C52" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D52" s="3">
         <v>0.14588888888888887</v>
@@ -2649,7 +2646,7 @@
         <v>33.701030538416305</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
@@ -2657,11 +2654,11 @@
         <v>14</v>
       </c>
       <c r="B53" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>L1</v>
       </c>
       <c r="C53" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D53" s="3">
         <v>0.18999999999999997</v>
@@ -2683,7 +2680,7 @@
         <v>28.469024237080394</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
@@ -2691,11 +2688,11 @@
         <v>16</v>
       </c>
       <c r="B54" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>L1</v>
       </c>
       <c r="C54" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D54" s="3">
         <v>0.17988888888888888</v>
@@ -2717,7 +2714,7 @@
         <v>26.820030596378835</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
@@ -2725,11 +2722,11 @@
         <v>17</v>
       </c>
       <c r="B55" t="str">
-        <f>IF(D55&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" ref="B55:B82" si="5">IF(D55&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
         <v>L1</v>
       </c>
       <c r="C55" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D55" s="3">
         <v>0.17277777777777778</v>
@@ -2751,7 +2748,7 @@
         <v>29.693921116269149</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
@@ -2759,11 +2756,11 @@
         <v>21</v>
       </c>
       <c r="B56" t="str">
-        <f>IF(D56&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L1</v>
       </c>
       <c r="C56" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D56" s="3">
         <v>0.18233333333333335</v>
@@ -2785,7 +2782,7 @@
         <v>28.432601363934481</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
@@ -2793,11 +2790,11 @@
         <v>23</v>
       </c>
       <c r="B57" t="str">
-        <f>IF(D57&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L1</v>
       </c>
       <c r="C57" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D57" s="3">
         <v>0.15744444444444444</v>
@@ -2819,7 +2816,7 @@
         <v>31.684490179081724</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
@@ -2827,11 +2824,11 @@
         <v>25</v>
       </c>
       <c r="B58" t="str">
-        <f>IF(D58&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L1</v>
       </c>
       <c r="C58" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D58" s="3">
         <v>0.15777777777777777</v>
@@ -2853,7 +2850,7 @@
         <v>33.500656963366666</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
@@ -2861,11 +2858,11 @@
         <v>29</v>
       </c>
       <c r="B59" t="str">
-        <f>IF(D59&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L1</v>
       </c>
       <c r="C59" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D59" s="3">
         <v>0.19533333333333336</v>
@@ -2887,7 +2884,7 @@
         <v>26.210357822661191</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
@@ -2895,11 +2892,11 @@
         <v>31</v>
       </c>
       <c r="B60" t="str">
-        <f>IF(D60&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L1</v>
       </c>
       <c r="C60" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D60" s="3">
         <v>0.19655555555555554</v>
@@ -2921,7 +2918,7 @@
         <v>25.537505618334997</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
@@ -2929,11 +2926,11 @@
         <v>34</v>
       </c>
       <c r="B61" t="str">
-        <f>IF(D61&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L1</v>
       </c>
       <c r="C61" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D61" s="3">
         <v>0.18622222222222218</v>
@@ -2955,7 +2952,7 @@
         <v>31.221896966321825</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
@@ -2963,11 +2960,11 @@
         <v>38</v>
       </c>
       <c r="B62" t="str">
-        <f>IF(D62&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L1</v>
       </c>
       <c r="C62" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D62" s="3">
         <v>0.16822222222222219</v>
@@ -2989,7 +2986,7 @@
         <v>31.797657777950075</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
@@ -2997,11 +2994,11 @@
         <v>46</v>
       </c>
       <c r="B63" t="str">
-        <f>IF(D63&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L1</v>
       </c>
       <c r="C63" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D63" s="3">
         <v>0.15922222222222221</v>
@@ -3023,7 +3020,7 @@
         <v>31.070829899463174</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
@@ -3031,11 +3028,11 @@
         <v>1</v>
       </c>
       <c r="B64" t="str">
-        <f>IF(D64&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C64" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D64" s="3">
         <v>0.25111111111111106</v>
@@ -3057,7 +3054,7 @@
         <v>20.494718060550284</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
@@ -3065,11 +3062,11 @@
         <v>41</v>
       </c>
       <c r="B65" t="str">
-        <f>IF(D65&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C65" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D65" s="3">
         <v>0.25422222222222224</v>
@@ -3091,7 +3088,7 @@
         <v>20.881142527977424</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
@@ -3099,11 +3096,11 @@
         <v>2</v>
       </c>
       <c r="B66" t="str">
-        <f>IF(D66&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C66" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D66" s="3">
         <v>0.31755555555555559</v>
@@ -3125,7 +3122,7 @@
         <v>17.659460456064075</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
@@ -3133,11 +3130,11 @@
         <v>5</v>
       </c>
       <c r="B67" t="str">
-        <f>IF(D67&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C67" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D67" s="3">
         <v>0.309</v>
@@ -3159,7 +3156,7 @@
         <v>17.126798471190362</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
@@ -3167,11 +3164,11 @@
         <v>6</v>
       </c>
       <c r="B68" t="str">
-        <f>IF(D68&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C68" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D68" s="3">
         <v>0.27977777777777779</v>
@@ -3193,7 +3190,7 @@
         <v>20.132157638933169</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
@@ -3201,11 +3198,11 @@
         <v>13</v>
       </c>
       <c r="B69" t="str">
-        <f>IF(D69&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C69" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D69" s="3">
         <v>0.36577777777777776</v>
@@ -3227,7 +3224,7 @@
         <v>13.76403983</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
@@ -3235,11 +3232,11 @@
         <v>19</v>
       </c>
       <c r="B70" t="str">
-        <f>IF(D70&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C70" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D70" s="3">
         <v>0.33533333333333332</v>
@@ -3261,7 +3258,7 @@
         <v>15.554052872301762</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
@@ -3269,11 +3266,11 @@
         <v>20</v>
       </c>
       <c r="B71" t="str">
-        <f>IF(D71&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C71" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D71" s="3">
         <v>0.2911111111111111</v>
@@ -3295,7 +3292,7 @@
         <v>20.333076705810427</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
@@ -3303,11 +3300,11 @@
         <v>22</v>
       </c>
       <c r="B72" t="str">
-        <f>IF(D72&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C72" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D72" s="3">
         <v>0.28444444444444444</v>
@@ -3329,7 +3326,7 @@
         <v>19.3058217626035</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
@@ -3337,11 +3334,11 @@
         <v>24</v>
       </c>
       <c r="B73" t="str">
-        <f>IF(D73&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C73" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D73" s="3">
         <v>0.2782222222222222</v>
@@ -3363,7 +3360,7 @@
         <v>19.713424079999999</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
@@ -3371,11 +3368,11 @@
         <v>26</v>
       </c>
       <c r="B74" t="str">
-        <f>IF(D74&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C74" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D74" s="3">
         <v>0.31211111111111112</v>
@@ -3397,7 +3394,7 @@
         <v>18.269771120969601</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
@@ -3405,11 +3402,11 @@
         <v>27</v>
       </c>
       <c r="B75" t="str">
-        <f>IF(D75&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C75" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D75" s="3">
         <v>0.31399999999999995</v>
@@ -3431,7 +3428,7 @@
         <v>16.691279120000001</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
@@ -3439,11 +3436,11 @@
         <v>30</v>
       </c>
       <c r="B76" t="str">
-        <f>IF(D76&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C76" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D76" s="3">
         <v>0.33311111111111108</v>
@@ -3452,7 +3449,7 @@
         <v>3.0184617127124746E-3</v>
       </c>
       <c r="F76" s="7">
-        <f t="shared" ref="F76:F107" si="4">(D76/2)^2 * PI()</f>
+        <f t="shared" ref="F76:F107" si="6">(D76/2)^2 * PI()</f>
         <v>8.7150146101344653E-2</v>
       </c>
       <c r="G76" s="5">
@@ -3465,7 +3462,7 @@
         <v>15.92657653730703</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
@@ -3473,11 +3470,11 @@
         <v>32</v>
       </c>
       <c r="B77" t="str">
-        <f>IF(D77&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C77" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D77" s="3">
         <v>0.32511111111111113</v>
@@ -3486,7 +3483,7 @@
         <v>4.4565806523736498E-3</v>
       </c>
       <c r="F77" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>8.3014413905818915E-2</v>
       </c>
       <c r="G77" s="5">
@@ -3499,7 +3496,7 @@
         <v>16.424021348958828</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
@@ -3507,11 +3504,11 @@
         <v>33</v>
       </c>
       <c r="B78" t="str">
-        <f>IF(D78&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C78" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D78" s="3">
         <v>0.28788888888888886</v>
@@ -3520,7 +3517,7 @@
         <v>2.5339911426662701E-2</v>
       </c>
       <c r="F78" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.5093809478654133E-2</v>
       </c>
       <c r="G78" s="5">
@@ -3533,7 +3530,7 @@
         <v>16.647920838877177</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
@@ -3541,11 +3538,11 @@
         <v>35</v>
       </c>
       <c r="B79" t="str">
-        <f>IF(D79&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C79" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D79" s="3">
         <v>0.29222222222222222</v>
@@ -3554,7 +3551,7 @@
         <v>1.4813657362192662E-3</v>
       </c>
       <c r="F79" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.7068155017330974E-2</v>
       </c>
       <c r="G79" s="5">
@@ -3567,7 +3564,7 @@
         <v>19.223406479568439</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
@@ -3575,11 +3572,11 @@
         <v>36</v>
       </c>
       <c r="B80" t="str">
-        <f>IF(D80&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C80" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D80" s="3">
         <v>0.2924444444444444</v>
@@ -3588,7 +3585,7 @@
         <v>6.6164777470930757E-3</v>
       </c>
       <c r="F80" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.7170198600930903E-2</v>
       </c>
       <c r="G80" s="5">
@@ -3601,7 +3598,7 @@
         <v>18.792476109232506</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
@@ -3609,11 +3606,11 @@
         <v>37</v>
       </c>
       <c r="B81" t="str">
-        <f>IF(D81&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C81" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D81" s="3">
         <v>0.33288888888888896</v>
@@ -3622,7 +3619,7 @@
         <v>6.9721668877839689E-3</v>
       </c>
       <c r="F81" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>8.7033907173161895E-2</v>
       </c>
       <c r="G81" s="5">
@@ -3635,7 +3632,7 @@
         <v>15.209573968864451</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
@@ -3643,11 +3640,11 @@
         <v>42</v>
       </c>
       <c r="B82" t="str">
-        <f>IF(D82&lt;AVERAGE($D$45:$D$82), "L1","L2")</f>
+        <f t="shared" si="5"/>
         <v>L2</v>
       </c>
       <c r="C82" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D82" s="3">
         <v>0.29099999999999998</v>
@@ -3656,7 +3653,7 @@
         <v>3.7080992435478345E-3</v>
       </c>
       <c r="F82" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.6508301874659309E-2</v>
       </c>
       <c r="G82" s="5">
@@ -3669,7 +3666,7 @@
         <v>18.995662746255732</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
@@ -3678,13 +3675,13 @@
         <v>F1</v>
       </c>
       <c r="C83" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D83" s="4">
         <v>4.552835220663428E-2</v>
       </c>
       <c r="F83" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.6279975462767258E-3</v>
       </c>
       <c r="G83" s="5">
@@ -3697,22 +3694,22 @@
         <v>22.176682848007978</v>
       </c>
       <c r="J83" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B84" t="str">
-        <f t="shared" ref="B84:B95" si="5">IF(D84&lt;AVERAGE($D$83:$D$95), "F1","F2")</f>
+        <f t="shared" ref="B84:B95" si="7">IF(D84&lt;AVERAGE($D$83:$D$95), "F1","F2")</f>
         <v>F1</v>
       </c>
       <c r="C84" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D84" s="4">
         <v>4.5416875834617329E-2</v>
       </c>
       <c r="F84" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.620034988000701E-3</v>
       </c>
       <c r="G84" s="5">
@@ -3725,22 +3722,22 @@
         <v>21.068753910865912</v>
       </c>
       <c r="J84" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B85" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>F1</v>
       </c>
       <c r="C85" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D85" s="4">
         <v>4.5416875834617329E-2</v>
       </c>
       <c r="F85" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.620034988000701E-3</v>
       </c>
       <c r="G85" s="5">
@@ -3753,22 +3750,22 @@
         <v>20.413788597658286</v>
       </c>
       <c r="J85" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B86" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>F1</v>
       </c>
       <c r="C86" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D86" s="4">
         <v>3.6525166666666664E-2</v>
       </c>
       <c r="F86" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.0477901079527588E-3</v>
       </c>
       <c r="G86" s="5">
@@ -3781,22 +3778,22 @@
         <v>17.14447943614557</v>
       </c>
       <c r="J86" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B87" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>F1</v>
       </c>
       <c r="C87" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D87" s="4">
         <v>4.8634411111111109E-2</v>
       </c>
       <c r="F87" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.8577069443885029E-3</v>
       </c>
       <c r="G87" s="5">
@@ -3809,22 +3806,22 @@
         <v>20.748205473341834</v>
       </c>
       <c r="J87" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B88" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>F1</v>
       </c>
       <c r="C88" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D88" s="4">
         <v>4.8634411111111109E-2</v>
       </c>
       <c r="F88" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.8577069443885029E-3</v>
       </c>
       <c r="G88" s="5">
@@ -3837,22 +3834,22 @@
         <v>20.644062741044163</v>
       </c>
       <c r="J88" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B89" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>F1</v>
       </c>
       <c r="C89" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D89" s="4">
         <v>4.0040936214592503E-2</v>
       </c>
       <c r="F89" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.2592104758060677E-3</v>
       </c>
       <c r="G89" s="5">
@@ -3865,22 +3862,22 @@
         <v>18.487127468855263</v>
       </c>
       <c r="J89" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B90" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>F2</v>
       </c>
       <c r="C90" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D90" s="4">
         <v>5.3566091996503168E-2</v>
       </c>
       <c r="F90" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.2535635369184738E-3</v>
       </c>
       <c r="G90" s="5">
@@ -3893,22 +3890,22 @@
         <v>16.834797305496142</v>
       </c>
       <c r="J90" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B91" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>F2</v>
       </c>
       <c r="C91" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D91" s="4">
         <v>5.3566091996503168E-2</v>
       </c>
       <c r="F91" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.2535635369184738E-3</v>
       </c>
       <c r="G91" s="5">
@@ -3921,22 +3918,22 @@
         <v>17.433486174601189</v>
       </c>
       <c r="J91" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B92" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>F2</v>
       </c>
       <c r="C92" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D92" s="4">
         <v>5.9822300000000002E-2</v>
       </c>
       <c r="F92" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.8107103585400979E-3</v>
       </c>
       <c r="G92" s="5">
@@ -3949,22 +3946,22 @@
         <v>17.733756347407969</v>
       </c>
       <c r="J92" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B93" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>F2</v>
       </c>
       <c r="C93" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D93" s="4">
         <v>6.0174449276210018E-2</v>
       </c>
       <c r="F93" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.8438987468366317E-3</v>
       </c>
       <c r="G93" s="5">
@@ -3977,22 +3974,22 @@
         <v>25.784364040262606</v>
       </c>
       <c r="J93" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B94" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>F2</v>
       </c>
       <c r="C94" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D94" s="4">
         <v>6.0174449276210018E-2</v>
       </c>
       <c r="F94" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.8438987468366317E-3</v>
       </c>
       <c r="G94" s="5">
@@ -4005,22 +4002,22 @@
         <v>24.193507973413883</v>
       </c>
       <c r="J94" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B95" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>F2</v>
       </c>
       <c r="C95" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D95" s="4">
         <v>7.1964342934999315E-2</v>
       </c>
       <c r="F95" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4.06747235858387E-3</v>
       </c>
       <c r="G95" s="5">
@@ -4033,7 +4030,7 @@
         <v>24.960974073635771</v>
       </c>
       <c r="J95" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
@@ -4042,14 +4039,14 @@
         <v>X2</v>
       </c>
       <c r="C96" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D96" s="3">
         <v>0.44185388817689258</v>
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.15333709929473427</v>
       </c>
       <c r="G96" s="5">
@@ -4062,23 +4059,23 @@
         <v>24.226382895819203</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" t="str">
-        <f t="shared" ref="B97:B108" si="6">IF(D97&lt;AVERAGE($D$96:$D$108), "X1","X2")</f>
+        <f t="shared" ref="B97:B108" si="8">IF(D97&lt;AVERAGE($D$96:$D$108), "X1","X2")</f>
         <v>X2</v>
       </c>
       <c r="C97" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D97" s="3">
         <v>0.31728998883112325</v>
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>7.9068339833408621E-2</v>
       </c>
       <c r="G97" s="5">
@@ -4091,23 +4088,23 @@
         <v>29.767682131711567</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>X2</v>
       </c>
       <c r="C98" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D98" s="3">
         <v>0.31728998883112325</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>7.9068339833408621E-2</v>
       </c>
       <c r="G98" s="5">
@@ -4120,23 +4117,23 @@
         <v>28.764518502713592</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>X2</v>
       </c>
       <c r="C99" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D99" s="3">
         <v>0.41977777777777781</v>
       </c>
       <c r="E99" s="4"/>
       <c r="F99" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.13839766715123686</v>
       </c>
       <c r="G99" s="5">
@@ -4149,23 +4146,23 @@
         <v>32.31573290692598</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B100" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>X1</v>
       </c>
       <c r="C100" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D100" s="3">
         <v>0.22577777777777777</v>
       </c>
       <c r="E100" s="4"/>
       <c r="F100" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4.0036146496592408E-2</v>
       </c>
       <c r="G100" s="5">
@@ -4178,23 +4175,23 @@
         <v>25.231275508386602</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>X1</v>
       </c>
       <c r="C101" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D101" s="3">
         <v>0.26955555555555555</v>
       </c>
       <c r="E101" s="4"/>
       <c r="F101" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5.7067185692836545E-2</v>
       </c>
       <c r="G101" s="5">
@@ -4207,23 +4204,23 @@
         <v>22.161352981139068</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>X1</v>
       </c>
       <c r="C102" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D102" s="3">
         <v>0.20355555555555557</v>
       </c>
       <c r="E102" s="4"/>
       <c r="F102" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3.2542866241363426E-2</v>
       </c>
       <c r="G102" s="5">
@@ -4236,23 +4233,23 @@
         <v>25.810365121258489</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B103" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>X1</v>
       </c>
       <c r="C103" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D103" s="3">
         <v>0.20266666666666666</v>
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3.2259269630461593E-2</v>
       </c>
       <c r="G103" s="5">
@@ -4265,23 +4262,23 @@
         <v>29.300197116378072</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B104" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>X1</v>
       </c>
       <c r="C104" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D104" s="3">
         <v>0.21622222222222226</v>
       </c>
       <c r="E104" s="4"/>
       <c r="F104" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3.6718973720251999E-2</v>
       </c>
       <c r="G104" s="5">
@@ -4294,23 +4291,23 @@
         <v>28.238980685964901</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B105" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>X1</v>
       </c>
       <c r="C105" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D105" s="3">
         <v>0.24733333333333332</v>
       </c>
       <c r="E105" s="4"/>
       <c r="F105" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4.8045772714750294E-2</v>
       </c>
       <c r="G105" s="5">
@@ -4323,23 +4320,23 @@
         <v>25.35499046132497</v>
       </c>
       <c r="J105" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B106" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>X2</v>
       </c>
       <c r="C106" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D106" s="3">
         <v>0.29888888888888887</v>
       </c>
       <c r="E106" s="4"/>
       <c r="F106" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>7.0163205557534261E-2</v>
       </c>
       <c r="G106" s="5">
@@ -4352,23 +4349,23 @@
         <v>22.962666191832824</v>
       </c>
       <c r="J106" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B107" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>X1</v>
       </c>
       <c r="C107" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D107" s="3">
         <v>0.23011111111111113</v>
       </c>
       <c r="E107" s="4"/>
       <c r="F107" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4.1587715112794507E-2</v>
       </c>
       <c r="G107" s="5">
@@ -4381,23 +4378,23 @@
         <v>24.460075709265517</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B108" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>X1</v>
       </c>
       <c r="C108" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D108" s="3">
         <v>0.23977777777777773</v>
       </c>
       <c r="E108" s="4"/>
       <c r="F108" s="7">
-        <f t="shared" ref="F108:F115" si="7">(D108/2)^2 * PI()</f>
+        <f t="shared" ref="F108:F115" si="9">(D108/2)^2 * PI()</f>
         <v>4.5155197192691766E-2</v>
       </c>
       <c r="G108" s="5">
@@ -4410,22 +4407,22 @@
         <v>22.791580620688187</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C109" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D109" s="3">
         <v>0.89755555555555544</v>
       </c>
       <c r="E109" s="4"/>
       <c r="F109" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.63272145342941732</v>
       </c>
       <c r="G109" s="5">
@@ -4438,22 +4435,22 @@
         <v>6.9046815176846152</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D110" s="3">
         <v>1.0513333333333332</v>
       </c>
       <c r="E110" s="4"/>
       <c r="F110" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.86810198626660107</v>
       </c>
       <c r="G110" s="5">
@@ -4466,22 +4463,22 @@
         <v>4.7766448072144421</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D111" s="3">
         <v>1.6924325554167357</v>
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2.2496379149378445</v>
       </c>
       <c r="G111" s="5">
@@ -4494,22 +4491,22 @@
         <v>3.1235457135457123</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C112" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D112" s="3">
         <v>1.6924325554167357</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2.2496379149378445</v>
       </c>
       <c r="G112" s="5">
@@ -4522,22 +4519,22 @@
         <v>3.4223828197945836</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B113" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C113" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D113" s="3">
         <v>1.6924325554167357</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2.2496379149378445</v>
       </c>
       <c r="G113" s="5">
@@ -4550,22 +4547,22 @@
         <v>3.2482967032967052</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C114" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D114" s="3">
         <v>1.5284444444444445</v>
       </c>
       <c r="E114" s="3"/>
       <c r="F114" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1.834801965908945</v>
       </c>
       <c r="G114" s="5">
@@ -4578,22 +4575,22 @@
         <v>3.771833763506387</v>
       </c>
       <c r="J114" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B115" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C115" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D115" s="3">
         <v>1.5284444444444445</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1.834801965908945</v>
       </c>
       <c r="G115" s="5">
@@ -4606,7 +4603,7 @@
         <v>4.1912240725918188</v>
       </c>
       <c r="J115" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.3">
@@ -4717,25 +4714,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" t="s">
         <v>124</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1" t="s">
         <v>119</v>
       </c>
-      <c r="D1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>120</v>
-      </c>
-      <c r="F1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -4743,7 +4740,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C2">
         <v>109.349222222222</v>
@@ -4767,7 +4764,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C3">
         <v>92.363</v>
@@ -4791,7 +4788,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C4">
         <v>88.398444444444465</v>
@@ -4815,7 +4812,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C5">
         <v>59.569888888888876</v>
@@ -4839,7 +4836,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C6">
         <v>100.65266666666668</v>
@@ -4863,7 +4860,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C7">
         <v>122.31700000000001</v>
@@ -4887,7 +4884,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C8">
         <v>160.96522222222222</v>
@@ -4911,7 +4908,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C9">
         <v>118.86566666666666</v>
@@ -4935,7 +4932,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C10">
         <v>76.555444444444447</v>
@@ -4959,7 +4956,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C11">
         <v>90.440666666666672</v>
